--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Parámetro</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Nº de carreras clasificatorias</t>
+  </si>
+  <si>
+    <t>Tiempo Eliminatorias</t>
   </si>
   <si>
     <t>Nº de equipos que se clasifican</t>
@@ -458,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,14 +541,22 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
         <v>45778.29166666667</v>
       </c>
     </row>
@@ -562,13 +573,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -576,10 +587,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -587,10 +598,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -598,10 +609,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -609,10 +620,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -620,10 +631,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>Parámetro</t>
   </si>
@@ -62,28 +62,58 @@
     <t>Categoria</t>
   </si>
   <si>
-    <t>Equipo A</t>
+    <t>Equipo Entry 1</t>
   </si>
   <si>
     <t>Entry</t>
   </si>
   <si>
-    <t>Equipo B</t>
-  </si>
-  <si>
-    <t>Equipo C</t>
+    <t>Equipo Entry 2</t>
+  </si>
+  <si>
+    <t>Equipo Entry 3</t>
+  </si>
+  <si>
+    <t>Equipo Entry 4</t>
+  </si>
+  <si>
+    <t>Equipo Entry 5</t>
+  </si>
+  <si>
+    <t>Equipo Development 1</t>
   </si>
   <si>
     <t>Development</t>
   </si>
   <si>
-    <t>Equipo D</t>
-  </si>
-  <si>
-    <t>Equipo E</t>
+    <t>Equipo Development 2</t>
+  </si>
+  <si>
+    <t>Equipo Development 3</t>
+  </si>
+  <si>
+    <t>Equipo Development 4</t>
+  </si>
+  <si>
+    <t>Equipo Development 5</t>
+  </si>
+  <si>
+    <t>Equipo Professional 1</t>
   </si>
   <si>
     <t>Professional</t>
+  </si>
+  <si>
+    <t>Equipo Professional 2</t>
+  </si>
+  <si>
+    <t>Equipo Professional 3</t>
+  </si>
+  <si>
+    <t>Equipo Professional 4</t>
+  </si>
+  <si>
+    <t>Equipo Professional 5</t>
   </si>
 </sst>
 </file>
@@ -477,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -485,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -493,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -549,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -568,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -612,7 +642,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -620,10 +650,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -631,10 +661,120 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>Parámetro</t>
   </si>
@@ -80,6 +80,27 @@
     <t>Equipo Entry 5</t>
   </si>
   <si>
+    <t>Equipo Entry 6</t>
+  </si>
+  <si>
+    <t>Equipo Entry 7</t>
+  </si>
+  <si>
+    <t>Equipo Entry 8</t>
+  </si>
+  <si>
+    <t>Equipo Entry 9</t>
+  </si>
+  <si>
+    <t>Equipo Entry 10</t>
+  </si>
+  <si>
+    <t>Equipo Entry 11</t>
+  </si>
+  <si>
+    <t>Equipo Entry 12</t>
+  </si>
+  <si>
     <t>Equipo Development 1</t>
   </si>
   <si>
@@ -98,6 +119,21 @@
     <t>Equipo Development 5</t>
   </si>
   <si>
+    <t>Equipo Development 6</t>
+  </si>
+  <si>
+    <t>Equipo Development 7</t>
+  </si>
+  <si>
+    <t>Equipo Development 8</t>
+  </si>
+  <si>
+    <t>Equipo Development 9</t>
+  </si>
+  <si>
+    <t>Equipo Development 10</t>
+  </si>
+  <si>
     <t>Equipo Professional 1</t>
   </si>
   <si>
@@ -114,6 +150,21 @@
   </si>
   <si>
     <t>Equipo Professional 5</t>
+  </si>
+  <si>
+    <t>Equipo Professional 6</t>
+  </si>
+  <si>
+    <t>Equipo Professional 7</t>
+  </si>
+  <si>
+    <t>Equipo Professional 8</t>
+  </si>
+  <si>
+    <t>Equipo Professional 9</t>
+  </si>
+  <si>
+    <t>Equipo Professional 10</t>
   </si>
 </sst>
 </file>
@@ -507,7 +558,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -515,7 +566,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -523,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -531,7 +582,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -539,7 +590,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -547,7 +598,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -555,7 +606,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -579,7 +630,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -598,7 +649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -675,7 +726,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,10 +734,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,10 +745,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,10 +756,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +767,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +778,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +789,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +800,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +811,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +822,197 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
   <si>
     <t>Parámetro</t>
   </si>
@@ -41,16 +41,43 @@
     <t>Nº de personal para el registro</t>
   </si>
   <si>
-    <t>Nº de carreras clasificatorias</t>
-  </si>
-  <si>
-    <t>Tiempo Eliminatorias</t>
-  </si>
-  <si>
-    <t>Nº de equipos que se clasifican</t>
-  </si>
-  <si>
-    <t>Fecha de inicio</t>
+    <t>Carreras Entry</t>
+  </si>
+  <si>
+    <t>Carreras Development</t>
+  </si>
+  <si>
+    <t>Carreras Professional</t>
+  </si>
+  <si>
+    <t>Nº de Días</t>
+  </si>
+  <si>
+    <t>Día 1</t>
+  </si>
+  <si>
+    <t>Inicio Día 1</t>
+  </si>
+  <si>
+    <t>Fin Día 1</t>
+  </si>
+  <si>
+    <t>Día 2</t>
+  </si>
+  <si>
+    <t>Inicio Día 2</t>
+  </si>
+  <si>
+    <t>Fin Día 2</t>
+  </si>
+  <si>
+    <t>Día 3</t>
+  </si>
+  <si>
+    <t>Inicio Día 3</t>
+  </si>
+  <si>
+    <t>Fin Día 3</t>
   </si>
   <si>
     <t>ID</t>
@@ -114,6 +141,12 @@
   </si>
   <si>
     <t>Equipo Professional 5</t>
+  </si>
+  <si>
+    <t>Equipo Professional 6</t>
+  </si>
+  <si>
+    <t>Equipo Professional 7</t>
   </si>
 </sst>
 </file>
@@ -491,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -523,7 +556,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -563,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -571,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -579,15 +612,87 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
-        <v>45778.29166666667</v>
+      <c r="B12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45825.58333333333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45825.58333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45825.70833333333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>45826.29166666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
+        <v>45826.29166666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>45826.66666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>45827.29166666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45827.29166666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
+        <v>45827.5</v>
       </c>
     </row>
   </sheetData>
@@ -598,18 +703,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,10 +733,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +744,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +755,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +766,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +777,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,10 +788,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,10 +799,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,10 +810,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +821,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +832,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +843,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +854,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +865,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +876,32 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -644,7 +644,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>45825.70833333333</v>
+        <v>45825.711805555555</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>Parámetro</t>
   </si>
@@ -29,10 +29,16 @@
     <t>Nº equipos de Professional</t>
   </si>
   <si>
+    <t>Nº de equipos que se clasifican</t>
+  </si>
+  <si>
     <t>Nº de Jueces para el portfolio técnico</t>
   </si>
   <si>
     <t>Nº de Jueces para el portfolio de empresa</t>
+  </si>
+  <si>
+    <t>Nº de Jueces para el escrutinio</t>
   </si>
   <si>
     <t>Nº de Jueces para la presentación verbal</t>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +570,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +586,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +594,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +610,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -612,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,23 +626,23 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
-        <v>45825.58333333333</v>
+      <c r="B13">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1">
-        <v>45825.58333333333</v>
+      <c r="B14">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +650,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>45825.711805555555</v>
+        <v>45825.58333333333</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,7 +658,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>45826.29166666667</v>
+        <v>45825.58333333333</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,7 +666,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>45826.29166666667</v>
+        <v>45825.711805555555</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -668,7 +674,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>45826.66666666667</v>
+        <v>45826.29166666667</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>45827.29166666667</v>
+        <v>45826.29166666667</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -684,7 +690,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>45827.29166666667</v>
+        <v>45826.66666666667</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -692,6 +698,22 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
+        <v>45827.29166666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>45827.29166666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1">
         <v>45827.5</v>
       </c>
     </row>
@@ -708,13 +730,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -722,10 +744,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -733,10 +755,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -744,10 +766,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -755,10 +777,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -766,10 +788,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -777,10 +799,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -788,10 +810,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -799,10 +821,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -810,10 +832,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -821,10 +843,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -832,10 +854,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -843,10 +865,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,10 +876,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -865,10 +887,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -876,10 +898,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -887,10 +909,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -898,10 +920,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
   <si>
     <t>Parámetro</t>
   </si>
@@ -56,34 +56,58 @@
     <t>Carreras Professional</t>
   </si>
   <si>
-    <t>Nº de Días</t>
-  </si>
-  <si>
-    <t>Día 1</t>
-  </si>
-  <si>
-    <t>Inicio Día 1</t>
-  </si>
-  <si>
-    <t>Fin Día 1</t>
-  </si>
-  <si>
-    <t>Día 2</t>
-  </si>
-  <si>
-    <t>Inicio Día 2</t>
-  </si>
-  <si>
-    <t>Fin Día 2</t>
-  </si>
-  <si>
-    <t>Día 3</t>
-  </si>
-  <si>
-    <t>Inicio Día 3</t>
-  </si>
-  <si>
-    <t>Fin Día 3</t>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>2025-06-17T07:00:00.000Z</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>2025-06-17T17:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Duración registro</t>
+  </si>
+  <si>
+    <t>Duración Charla/Presentación</t>
+  </si>
+  <si>
+    <t>Duración Montaje del Pit Display</t>
+  </si>
+  <si>
+    <t>Duración Escrutinio Entry</t>
+  </si>
+  <si>
+    <t>Duración Escrutinio Development</t>
+  </si>
+  <si>
+    <t>Duración Escrutinio Professional</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Técnico Entry</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Técnico Development</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Técnico Professional</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Empresa Entry</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Empresa Development</t>
+  </si>
+  <si>
+    <t>Duración Portfolio Empresa Professional</t>
+  </si>
+  <si>
+    <t>Duración Presentación Verbal Entry</t>
+  </si>
+  <si>
+    <t>Duración Ceremonia de Clausura y Premios</t>
   </si>
   <si>
     <t>ID</t>
@@ -113,6 +137,21 @@
     <t>Equipo Entry 5</t>
   </si>
   <si>
+    <t>Equipo Entry 6</t>
+  </si>
+  <si>
+    <t>Equipo Entry 7</t>
+  </si>
+  <si>
+    <t>Equipo Entry 8</t>
+  </si>
+  <si>
+    <t>Equipo Entry 9</t>
+  </si>
+  <si>
+    <t>Equipo Entry 10</t>
+  </si>
+  <si>
     <t>Equipo Development 1</t>
   </si>
   <si>
@@ -131,6 +170,21 @@
     <t>Equipo Development 5</t>
   </si>
   <si>
+    <t>Equipo Development 6</t>
+  </si>
+  <si>
+    <t>Equipo Development 7</t>
+  </si>
+  <si>
+    <t>Equipo Development 8</t>
+  </si>
+  <si>
+    <t>Equipo Development 9</t>
+  </si>
+  <si>
+    <t>Equipo Development 10</t>
+  </si>
+  <si>
     <t>Equipo Professional 1</t>
   </si>
   <si>
@@ -153,6 +207,15 @@
   </si>
   <si>
     <t>Equipo Professional 7</t>
+  </si>
+  <si>
+    <t>Equipo Professional 8</t>
+  </si>
+  <si>
+    <t>Equipo Professional 9</t>
+  </si>
+  <si>
+    <t>Equipo Professional 10</t>
   </si>
 </sst>
 </file>
@@ -188,9 +251,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -562,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -641,80 +703,144 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>3</v>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
-        <v>45825.58333333333</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
-        <v>45825.58333333333</v>
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1">
-        <v>45825.711805555555</v>
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1">
-        <v>45826.29166666667</v>
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1">
-        <v>45826.29166666667</v>
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
         <v>20</v>
-      </c>
-      <c r="B20" s="1">
-        <v>45826.66666666667</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="1">
-        <v>45827.29166666667</v>
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1">
-        <v>45827.29166666667</v>
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="1">
-        <v>45827.5</v>
+        <v>25</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -725,18 +851,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -744,10 +870,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -755,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -766,10 +892,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -777,10 +903,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -788,10 +914,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -799,10 +925,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -810,10 +936,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -821,10 +947,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -832,10 +958,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -843,10 +969,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,10 +980,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -865,10 +991,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -876,10 +1002,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -887,10 +1013,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -898,10 +1024,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -909,10 +1035,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -920,10 +1046,153 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>Parámetro</t>
   </si>
@@ -56,16 +56,43 @@
     <t>Carreras Professional</t>
   </si>
   <si>
-    <t>StartDate</t>
+    <t>NumberOfDays</t>
+  </si>
+  <si>
+    <t>Dia 1 Start</t>
   </si>
   <si>
     <t>2025-06-17T07:00:00.000Z</t>
   </si>
   <si>
-    <t>EndDate</t>
-  </si>
-  <si>
-    <t>2025-06-17T17:00:00.000Z</t>
+    <t>Dia 1 End</t>
+  </si>
+  <si>
+    <t>2025-06-17T12:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Dia 2 Start</t>
+  </si>
+  <si>
+    <t>2025-06-18T07:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Dia 2 End</t>
+  </si>
+  <si>
+    <t>2025-06-18T10:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Dia 3 Start</t>
+  </si>
+  <si>
+    <t>2025-06-19T07:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Dia 3 End</t>
+  </si>
+  <si>
+    <t>2025-06-19T17:00:00.000Z</t>
   </si>
   <si>
     <t>Duración registro</t>
@@ -107,7 +134,19 @@
     <t>Duración Presentación Verbal Entry</t>
   </si>
   <si>
+    <t>Duración Presentación Verbal Development</t>
+  </si>
+  <si>
+    <t>Duración Presentación Verbal Professional</t>
+  </si>
+  <si>
     <t>Duración Ceremonia de Clausura y Premios</t>
+  </si>
+  <si>
+    <t>Duración Carrera</t>
+  </si>
+  <si>
+    <t>Tiempo Eliminatorias</t>
   </si>
   <si>
     <t>ID</t>
@@ -592,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -703,85 +742,85 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
-        <v>15</v>
+      <c r="B14">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
         <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
         <v>18</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
-        <v>30</v>
+      <c r="B17" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>60</v>
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>15</v>
@@ -789,39 +828,39 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>15</v>
@@ -829,18 +868,74 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B31">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36">
         <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -856,13 +951,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,10 +965,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,10 +976,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,10 +987,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +998,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +1009,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +1020,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,10 +1031,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,10 +1042,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -958,10 +1053,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,10 +1064,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,10 +1075,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -991,10 +1086,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1002,10 +1097,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,10 +1108,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,10 +1130,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,10 +1141,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,10 +1152,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,10 +1163,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,10 +1174,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1090,10 +1185,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,10 +1196,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,10 +1207,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1123,10 +1218,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,10 +1229,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1145,10 +1240,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,10 +1251,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1167,10 +1262,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,10 +1273,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1189,10 +1284,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -68,7 +68,7 @@
     <t>Dia 1 End</t>
   </si>
   <si>
-    <t>2025-06-17T12:00:00.000Z</t>
+    <t>2025-06-17T17:00:00.000Z</t>
   </si>
   <si>
     <t>Dia 2 Start</t>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="161">
   <si>
     <t>Parámetro</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Dia 2 End</t>
   </si>
   <si>
-    <t>2025-06-18T10:00:00.000Z</t>
+    <t>2025-06-18T17:00:00.000Z</t>
   </si>
   <si>
     <t>Dia 3 Start</t>
@@ -191,6 +191,96 @@
     <t>Equipo Entry 10</t>
   </si>
   <si>
+    <t>Equipo Entry 11</t>
+  </si>
+  <si>
+    <t>Equipo Entry 12</t>
+  </si>
+  <si>
+    <t>Equipo Entry 13</t>
+  </si>
+  <si>
+    <t>Equipo Entry 14</t>
+  </si>
+  <si>
+    <t>Equipo Entry 15</t>
+  </si>
+  <si>
+    <t>Equipo Entry 16</t>
+  </si>
+  <si>
+    <t>Equipo Entry 17</t>
+  </si>
+  <si>
+    <t>Equipo Entry 18</t>
+  </si>
+  <si>
+    <t>Equipo Entry 19</t>
+  </si>
+  <si>
+    <t>Equipo Entry 20</t>
+  </si>
+  <si>
+    <t>Equipo Entry 21</t>
+  </si>
+  <si>
+    <t>Equipo Entry 22</t>
+  </si>
+  <si>
+    <t>Equipo Entry 23</t>
+  </si>
+  <si>
+    <t>Equipo Entry 24</t>
+  </si>
+  <si>
+    <t>Equipo Entry 25</t>
+  </si>
+  <si>
+    <t>Equipo Entry 26</t>
+  </si>
+  <si>
+    <t>Equipo Entry 27</t>
+  </si>
+  <si>
+    <t>Equipo Entry 28</t>
+  </si>
+  <si>
+    <t>Equipo Entry 29</t>
+  </si>
+  <si>
+    <t>Equipo Entry 30</t>
+  </si>
+  <si>
+    <t>Equipo Entry 31</t>
+  </si>
+  <si>
+    <t>Equipo Entry 32</t>
+  </si>
+  <si>
+    <t>Equipo Entry 33</t>
+  </si>
+  <si>
+    <t>Equipo Entry 34</t>
+  </si>
+  <si>
+    <t>Equipo Entry 35</t>
+  </si>
+  <si>
+    <t>Equipo Entry 36</t>
+  </si>
+  <si>
+    <t>Equipo Entry 37</t>
+  </si>
+  <si>
+    <t>Equipo Entry 38</t>
+  </si>
+  <si>
+    <t>Equipo Entry 39</t>
+  </si>
+  <si>
+    <t>Equipo Entry 40</t>
+  </si>
+  <si>
     <t>Equipo Development 1</t>
   </si>
   <si>
@@ -224,6 +314,96 @@
     <t>Equipo Development 10</t>
   </si>
   <si>
+    <t>Equipo Development 11</t>
+  </si>
+  <si>
+    <t>Equipo Development 12</t>
+  </si>
+  <si>
+    <t>Equipo Development 13</t>
+  </si>
+  <si>
+    <t>Equipo Development 14</t>
+  </si>
+  <si>
+    <t>Equipo Development 15</t>
+  </si>
+  <si>
+    <t>Equipo Development 16</t>
+  </si>
+  <si>
+    <t>Equipo Development 17</t>
+  </si>
+  <si>
+    <t>Equipo Development 18</t>
+  </si>
+  <si>
+    <t>Equipo Development 19</t>
+  </si>
+  <si>
+    <t>Equipo Development 20</t>
+  </si>
+  <si>
+    <t>Equipo Development 21</t>
+  </si>
+  <si>
+    <t>Equipo Development 22</t>
+  </si>
+  <si>
+    <t>Equipo Development 23</t>
+  </si>
+  <si>
+    <t>Equipo Development 24</t>
+  </si>
+  <si>
+    <t>Equipo Development 25</t>
+  </si>
+  <si>
+    <t>Equipo Development 26</t>
+  </si>
+  <si>
+    <t>Equipo Development 27</t>
+  </si>
+  <si>
+    <t>Equipo Development 28</t>
+  </si>
+  <si>
+    <t>Equipo Development 29</t>
+  </si>
+  <si>
+    <t>Equipo Development 30</t>
+  </si>
+  <si>
+    <t>Equipo Development 31</t>
+  </si>
+  <si>
+    <t>Equipo Development 32</t>
+  </si>
+  <si>
+    <t>Equipo Development 33</t>
+  </si>
+  <si>
+    <t>Equipo Development 34</t>
+  </si>
+  <si>
+    <t>Equipo Development 35</t>
+  </si>
+  <si>
+    <t>Equipo Development 36</t>
+  </si>
+  <si>
+    <t>Equipo Development 37</t>
+  </si>
+  <si>
+    <t>Equipo Development 38</t>
+  </si>
+  <si>
+    <t>Equipo Development 39</t>
+  </si>
+  <si>
+    <t>Equipo Development 40</t>
+  </si>
+  <si>
     <t>Equipo Professional 1</t>
   </si>
   <si>
@@ -255,6 +435,66 @@
   </si>
   <si>
     <t>Equipo Professional 10</t>
+  </si>
+  <si>
+    <t>Equipo Professional 11</t>
+  </si>
+  <si>
+    <t>Equipo Professional 12</t>
+  </si>
+  <si>
+    <t>Equipo Professional 13</t>
+  </si>
+  <si>
+    <t>Equipo Professional 14</t>
+  </si>
+  <si>
+    <t>Equipo Professional 15</t>
+  </si>
+  <si>
+    <t>Equipo Professional 16</t>
+  </si>
+  <si>
+    <t>Equipo Professional 17</t>
+  </si>
+  <si>
+    <t>Equipo Professional 18</t>
+  </si>
+  <si>
+    <t>Equipo Professional 19</t>
+  </si>
+  <si>
+    <t>Equipo Professional 20</t>
+  </si>
+  <si>
+    <t>Equipo Professional 21</t>
+  </si>
+  <si>
+    <t>Equipo Professional 22</t>
+  </si>
+  <si>
+    <t>Equipo Professional 23</t>
+  </si>
+  <si>
+    <t>Equipo Professional 24</t>
+  </si>
+  <si>
+    <t>Equipo Professional 25</t>
+  </si>
+  <si>
+    <t>Equipo Professional 26</t>
+  </si>
+  <si>
+    <t>Equipo Professional 27</t>
+  </si>
+  <si>
+    <t>Equipo Professional 28</t>
+  </si>
+  <si>
+    <t>Equipo Professional 29</t>
+  </si>
+  <si>
+    <t>Equipo Professional 30</t>
   </si>
 </sst>
 </file>
@@ -647,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -655,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -663,7 +903,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1078,7 +1318,7 @@
         <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1086,10 +1326,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,10 +1337,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,10 +1348,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,10 +1359,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,10 +1370,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,10 +1381,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1392,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,10 +1403,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1174,10 +1414,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,10 +1425,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1196,10 +1436,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1207,10 +1447,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1218,10 +1458,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,10 +1469,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1240,10 +1480,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1251,10 +1491,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1262,10 +1502,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1273,10 +1513,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1284,10 +1524,890 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>118</v>
+      </c>
+      <c r="C70" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>124</v>
+      </c>
+      <c r="C76" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>132</v>
+      </c>
+      <c r="C83" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>133</v>
+      </c>
+      <c r="C84" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>134</v>
+      </c>
+      <c r="C85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>138</v>
+      </c>
+      <c r="C89" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>139</v>
+      </c>
+      <c r="C90" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>140</v>
+      </c>
+      <c r="C91" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>143</v>
+      </c>
+      <c r="C94" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>144</v>
+      </c>
+      <c r="C95" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>146</v>
+      </c>
+      <c r="C97" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>147</v>
+      </c>
+      <c r="C98" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>148</v>
+      </c>
+      <c r="C99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>149</v>
+      </c>
+      <c r="C100" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C101" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>151</v>
+      </c>
+      <c r="C102" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>152</v>
+      </c>
+      <c r="C103" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>153</v>
+      </c>
+      <c r="C104" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>154</v>
+      </c>
+      <c r="C105" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>155</v>
+      </c>
+      <c r="C106" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>156</v>
+      </c>
+      <c r="C107" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>157</v>
+      </c>
+      <c r="C108" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>158</v>
+      </c>
+      <c r="C109" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>159</v>
+      </c>
+      <c r="C110" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>160</v>
+      </c>
+      <c r="C111" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
   <si>
     <t>Parámetro</t>
   </si>
@@ -134,6 +134,15 @@
     <t>Duración Presentación Verbal Entry</t>
   </si>
   <si>
+    <t>Duración Carrera Entry</t>
+  </si>
+  <si>
+    <t>Duración Carrera Development</t>
+  </si>
+  <si>
+    <t>Duración Carrera Professional</t>
+  </si>
+  <si>
     <t>Duración Presentación Verbal Development</t>
   </si>
   <si>
@@ -141,9 +150,6 @@
   </si>
   <si>
     <t>Duración Ceremonia de Clausura y Premios</t>
-  </si>
-  <si>
-    <t>Duración Carrera</t>
   </si>
   <si>
     <t>Tiempo Eliminatorias</t>
@@ -634,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -906,7 +912,7 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -914,7 +920,7 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -922,7 +928,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -930,7 +936,7 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -938,7 +944,7 @@
         <v>44</v>
       </c>
       <c r="B38">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,6 +952,22 @@
         <v>45</v>
       </c>
       <c r="B39">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
         <v>2</v>
       </c>
     </row>
@@ -962,13 +984,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -976,10 +998,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -987,10 +1009,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -998,10 +1020,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1009,10 +1031,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1020,10 +1042,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,10 +1053,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,10 +1064,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,10 +1075,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1064,10 +1086,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1075,10 +1097,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1086,10 +1108,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,10 +1119,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,10 +1130,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,10 +1141,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,10 +1152,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,10 +1163,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1174,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,10 +1185,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1174,10 +1196,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,10 +1207,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1196,10 +1218,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1207,10 +1229,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1218,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,10 +1251,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1240,10 +1262,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1251,10 +1273,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1262,10 +1284,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1273,10 +1295,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1284,10 +1306,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1295,10 +1317,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/dummy-input.xlsx
+++ b/dummy-input.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
   <si>
     <t>Parámetro</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>2025-06-19T17:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Descanso Comida Dia 1 Start</t>
+  </si>
+  <si>
+    <t>2025-06-17T12:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Descanso Comida Dia 1 End</t>
+  </si>
+  <si>
+    <t>2025-06-17T14:00:00.000Z</t>
   </si>
   <si>
     <t>Duración registro</t>
@@ -640,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -807,85 +819,85 @@
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21">
-        <v>5</v>
+      <c r="B21" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24">
         <v>30</v>
-      </c>
-      <c r="B24">
-        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>15</v>
@@ -893,15 +905,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>15</v>
@@ -909,65 +921,81 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43">
         <v>2</v>
       </c>
     </row>
@@ -984,13 +1012,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -998,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1009,10 +1037,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1020,10 +1048,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,10 +1059,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,10 +1070,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,10 +1081,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1064,10 +1092,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1075,10 +1103,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1086,10 +1114,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,10 +1125,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,10 +1136,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,10 +1147,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,10 +1158,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,10 +1169,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1180,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
         <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,10 +1191,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1174,10 +1202,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,10 +1213,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1196,10 +1224,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1207,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1218,10 +1246,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,10 +1257,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1240,10 +1268,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1251,10 +1279,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1262,10 +1290,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1273,10 +1301,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1284,10 +1312,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1295,10 +1323,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1306,10 +1334,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1317,10 +1345,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
